--- a/GameConfig/Datas/_import_v1_preview/叙事物品配置表.xlsx
+++ b/GameConfig/Datas/_import_v1_preview/叙事物品配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -570,7 +570,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_glasses</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_camera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>narrative_clock</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>scene_chenguo_cat_broken</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
